--- a/outputs/february.xlsx
+++ b/outputs/february.xlsx
@@ -8182,7 +8182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP16"/>
+  <dimension ref="A1:BA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8366,6 +8366,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8492,6 +8537,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="AT2" s="1" t="n">
+        <v>65531.1</v>
+      </c>
+      <c r="AU2" s="1" t="n">
+        <v>-1944.49</v>
+      </c>
+      <c r="AV2" s="2" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="AW2" s="1" t="n">
+        <v>67440.98</v>
+      </c>
+      <c r="AX2" s="1" t="n">
+        <v>68135.99000000001</v>
+      </c>
+      <c r="AY2" s="1" t="n">
+        <v>65190.54</v>
+      </c>
+      <c r="AZ2" s="3" t="n">
+        <v>204695021</v>
+      </c>
+      <c r="BA2" s="4" t="inlineStr">
+        <is>
+          <t>02/27/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8575,9 +8651,7 @@
       <c r="AC3" s="1" t="n">
         <v>97.62</v>
       </c>
-      <c r="AD3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="AD3" s="3" t="n"/>
       <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>17:38 ET</t>
@@ -8606,12 +8680,41 @@
       <c r="AN3" s="1" t="n">
         <v>97.48999999999999</v>
       </c>
-      <c r="AO3" s="3" t="n">
+      <c r="AO3" s="3" t="n"/>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>17:38 ET</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AV3" s="2" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>97.84999999999999</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
         <v/>
       </c>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>17:38 ET</t>
+      <c r="BA3" s="4" t="inlineStr">
+        <is>
+          <t>02/27/26</t>
         </is>
       </c>
     </row>
@@ -8740,6 +8843,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>0.87614</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>0.00111</v>
+      </c>
+      <c r="AV4" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>0.87892</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>0.87458</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>490284</v>
+      </c>
+      <c r="BA4" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8866,6 +9000,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="AV5" s="2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>0.5461</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v>782422</v>
+      </c>
+      <c r="BA5" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8992,6 +9157,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>1.36431</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>-0.00386</v>
+      </c>
+      <c r="AV6" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>1.36816</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>1.36861</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>1.36252</v>
+      </c>
+      <c r="AZ6" s="3" t="n">
+        <v>298195</v>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9118,6 +9314,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>0.97073</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>-0.00148</v>
+      </c>
+      <c r="AV7" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>0.97453</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>0.9694</v>
+      </c>
+      <c r="AZ7" s="3" t="n">
+        <v>325328</v>
+      </c>
+      <c r="BA7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9244,6 +9471,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="AV8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AZ8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="BA8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9370,6 +9628,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AV9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AZ9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="BA9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9496,6 +9785,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>93.78100000000001</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>5.477</v>
+      </c>
+      <c r="AV10" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>88.304</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>94.133</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>87.88800000000001</v>
+      </c>
+      <c r="AZ10" s="3" t="n">
+        <v>186335</v>
+      </c>
+      <c r="BA10" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9622,6 +9942,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>5278.32</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="AV11" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>5185.29</v>
+      </c>
+      <c r="AX11" s="1" t="n">
+        <v>5280.79</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>5167.37</v>
+      </c>
+      <c r="AZ11" s="3" t="n">
+        <v>161365</v>
+      </c>
+      <c r="BA11" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9748,6 +10099,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="AV12" s="2" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>0.5658</v>
+      </c>
+      <c r="AX12" s="1" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="AY12" s="1" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="AZ12" s="3" t="n">
+        <v>266875</v>
+      </c>
+      <c r="BA12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9874,6 +10256,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>1.61205</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>-0.00201</v>
+      </c>
+      <c r="AV13" s="2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>1.61406</v>
+      </c>
+      <c r="AX13" s="1" t="n">
+        <v>1.61576</v>
+      </c>
+      <c r="AY13" s="1" t="n">
+        <v>1.60993</v>
+      </c>
+      <c r="AZ13" s="3" t="n">
+        <v>362347</v>
+      </c>
+      <c r="BA13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10000,6 +10413,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>156.056</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AV14" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>156.136</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>156.234</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>155.539</v>
+      </c>
+      <c r="AZ14" s="3" t="n">
+        <v>486904</v>
+      </c>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10126,6 +10570,37 @@
           <t>02/26/26</t>
         </is>
       </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>0.90892</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>-0.00432</v>
+      </c>
+      <c r="AV15" s="2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>0.91325</v>
+      </c>
+      <c r="AX15" s="1" t="n">
+        <v>0.91395</v>
+      </c>
+      <c r="AY15" s="1" t="n">
+        <v>0.90611</v>
+      </c>
+      <c r="AZ15" s="3" t="n">
+        <v>367572</v>
+      </c>
+      <c r="BA15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10250,6 +10725,37 @@
       <c r="AP16" s="4" t="inlineStr">
         <is>
           <t>02/26/26</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="AT16" s="1" t="n">
+        <v>0.76945</v>
+      </c>
+      <c r="AU16" s="1" t="n">
+        <v>-0.00466</v>
+      </c>
+      <c r="AV16" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>0.7741</v>
+      </c>
+      <c r="AX16" s="1" t="n">
+        <v>0.7745300000000001</v>
+      </c>
+      <c r="AY16" s="1" t="n">
+        <v>0.76717</v>
+      </c>
+      <c r="AZ16" s="3" t="n">
+        <v>335500</v>
+      </c>
+      <c r="BA16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
         </is>
       </c>
     </row>

--- a/outputs/february.xlsx
+++ b/outputs/february.xlsx
@@ -8709,9 +8709,7 @@
       <c r="AY3" s="1" t="n">
         <v>97.56</v>
       </c>
-      <c r="AZ3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="AZ3" s="3" t="n"/>
       <c r="BA3" s="4" t="inlineStr">
         <is>
           <t>02/27/26</t>
